--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcCapAssetInfo001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcCapAssetInfo001.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="1575" windowWidth="14805" windowHeight="5940" tabRatio="634"/>
+    <workbookView xWindow="240" yWindow="1572" windowWidth="14808" windowHeight="5940" tabRatio="634"/>
   </bookViews>
   <sheets>
     <sheet name="人行资金信托代码导入导出模板" sheetId="12" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>资产代码*</t>
+    <t>行内资产/负债编码*</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -440,14 +440,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C32"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="22.75" style="3" customWidth="1"/>
-    <col min="3" max="3" width="22.375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="21.109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="22.77734375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="22.33203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -458,157 +458,157 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -622,7 +622,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -633,7 +633,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
